--- a/Documentos/Horario Derek Lamy.xlsx
+++ b/Documentos/Horario Derek Lamy.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\energ\OneDrive\Escritorio\Sistemas\Multisports\Documentos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E3C2C89-8AA0-473D-B082-564D6457DC3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37C4624F-043A-4545-AF68-E2BDD854BA64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{6584DFC2-EEE0-4CD6-8176-87F5640B2F74}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{6584DFC2-EEE0-4CD6-8176-87F5640B2F74}"/>
   </bookViews>
   <sheets>
     <sheet name="1er Bimestre" sheetId="1" r:id="rId1"/>
     <sheet name="2do Bimestre" sheetId="2" r:id="rId2"/>
+    <sheet name="3er Bimestre" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="87">
   <si>
     <t>Tarea</t>
   </si>
@@ -242,6 +243,51 @@
   </si>
   <si>
     <t>Apartado meramente estético…</t>
+  </si>
+  <si>
+    <t>Arreglar dispocisiones</t>
+  </si>
+  <si>
+    <t>Arreglar IA</t>
+  </si>
+  <si>
+    <t>Volley</t>
+  </si>
+  <si>
+    <t>Aparatdo Gráfico , decorar…</t>
+  </si>
+  <si>
+    <t>Objetivo 1: Diseño e interfaz de usuario (UI/UX)</t>
+  </si>
+  <si>
+    <t>Tarea 1.1: Rediseño visual de las pantallas</t>
+  </si>
+  <si>
+    <t>Tarea 1.2: Agregar iconos y fondos alusivos a cada deporte</t>
+  </si>
+  <si>
+    <t>Tarea1.3: Unificar diseño y botones en todos los deportes</t>
+  </si>
+  <si>
+    <t>Objetivo 2: Implementación de Volleyball</t>
+  </si>
+  <si>
+    <t>Tarea 2.1: Crear módulo de Volleyball</t>
+  </si>
+  <si>
+    <t>Tarea 2.2: Implementar marcador oficial</t>
+  </si>
+  <si>
+    <t>Tarea 2.3: Agregar torneos y estadísticas</t>
+  </si>
+  <si>
+    <t>Tarea 3.1: Adaptación al entorno deportivo del ITC</t>
+  </si>
+  <si>
+    <t>Tarea 3.2: Personalizar reglas de baloncesto</t>
+  </si>
+  <si>
+    <t>Tarea 3.3: Configuración de deportes institucionales</t>
   </si>
 </sst>
 </file>
@@ -1509,7 +1555,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAC05EEE-74E6-4599-9D3A-032918F0ADDA}">
-  <dimension ref="A4:T26"/>
+  <dimension ref="A4:T31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="44.85546875" customWidth="1"/>
@@ -1655,9 +1701,9 @@
       <c r="F8" s="15"/>
       <c r="G8" s="15"/>
       <c r="H8" s="15"/>
-      <c r="I8" s="23"/>
-      <c r="J8" s="23"/>
-      <c r="K8" s="23"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
       <c r="L8" s="18"/>
       <c r="M8" s="18"/>
       <c r="N8" s="18"/>
@@ -1681,13 +1727,13 @@
       <c r="E9" s="17"/>
       <c r="F9" s="15"/>
       <c r="G9" s="15"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="23"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
       <c r="J9" s="18"/>
       <c r="K9" s="18"/>
       <c r="L9" s="18"/>
       <c r="M9" s="18"/>
-      <c r="N9" s="23"/>
+      <c r="N9" s="15"/>
       <c r="P9" t="s">
         <v>61</v>
       </c>
@@ -1779,7 +1825,7 @@
       </c>
       <c r="E13" s="17"/>
       <c r="F13" s="15"/>
-      <c r="G13" s="23" t="s">
+      <c r="G13" s="15" t="s">
         <v>15</v>
       </c>
       <c r="H13" s="18"/>
@@ -1787,8 +1833,8 @@
       <c r="J13" s="18"/>
       <c r="K13" s="18"/>
       <c r="L13" s="18"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="23" t="s">
+      <c r="M13" s="15"/>
+      <c r="N13" s="15" t="s">
         <v>15</v>
       </c>
       <c r="P13" t="s">
@@ -1957,6 +2003,28 @@
       </c>
       <c r="Q26" s="22"/>
       <c r="R26" s="22"/>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="P28" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q28" s="22"/>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="P29" s="22" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="P30" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q30" s="22"/>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="P31" s="22" t="s">
+        <v>74</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -2079,6 +2147,482 @@
             </x14:dataBar>
           </x14:cfRule>
           <xm:sqref>C19</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80A7E6DF-9919-4C0A-9568-58E6A58F64C4}">
+  <dimension ref="A4:N17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="54.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="N4" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="11">
+        <v>46204</v>
+      </c>
+      <c r="G5" s="11">
+        <v>46211</v>
+      </c>
+      <c r="H5" s="11">
+        <v>46218</v>
+      </c>
+      <c r="I5" s="11">
+        <v>46225</v>
+      </c>
+      <c r="J5" s="11">
+        <v>46232</v>
+      </c>
+      <c r="K5" s="11">
+        <v>46239</v>
+      </c>
+      <c r="L5" s="11">
+        <v>46246</v>
+      </c>
+      <c r="M5" s="11">
+        <v>46253</v>
+      </c>
+      <c r="N5" s="11">
+        <v>46260</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="23"/>
+      <c r="L6" s="23"/>
+      <c r="M6" s="23"/>
+      <c r="N6" s="23"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="15">
+        <v>90</v>
+      </c>
+      <c r="D7" s="16">
+        <v>46204</v>
+      </c>
+      <c r="E7" s="16">
+        <v>46260</v>
+      </c>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="23"/>
+      <c r="J7" s="23"/>
+      <c r="K7" s="23"/>
+      <c r="L7" s="23"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="23"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="15">
+        <v>100</v>
+      </c>
+      <c r="D8" s="16">
+        <v>46204</v>
+      </c>
+      <c r="E8" s="16">
+        <v>46260</v>
+      </c>
+      <c r="F8" s="23"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="23"/>
+      <c r="L8" s="23"/>
+      <c r="M8" s="23"/>
+      <c r="N8" s="23"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="15">
+        <v>90</v>
+      </c>
+      <c r="D9" s="16">
+        <v>46204</v>
+      </c>
+      <c r="E9" s="16">
+        <v>46260</v>
+      </c>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="18"/>
+      <c r="L9" s="23"/>
+      <c r="M9" s="23"/>
+      <c r="N9" s="23"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="23"/>
+      <c r="I10" s="23"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="23"/>
+      <c r="L10" s="23"/>
+      <c r="M10" s="23"/>
+      <c r="N10" s="23"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="15">
+        <v>20</v>
+      </c>
+      <c r="D11" s="16">
+        <v>46204</v>
+      </c>
+      <c r="E11" s="16">
+        <v>46260</v>
+      </c>
+      <c r="F11" s="23"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="23"/>
+      <c r="I11" s="23"/>
+      <c r="J11" s="23"/>
+      <c r="K11" s="18"/>
+      <c r="L11" s="18"/>
+      <c r="M11" s="18"/>
+      <c r="N11" s="18"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="15">
+        <v>0</v>
+      </c>
+      <c r="D12" s="16">
+        <v>46204</v>
+      </c>
+      <c r="E12" s="16">
+        <v>46260</v>
+      </c>
+      <c r="F12" s="23"/>
+      <c r="G12" s="23"/>
+      <c r="H12" s="23"/>
+      <c r="I12" s="23"/>
+      <c r="J12" s="23"/>
+      <c r="K12" s="18"/>
+      <c r="L12" s="18"/>
+      <c r="M12" s="18"/>
+      <c r="N12" s="18"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="15">
+        <v>0</v>
+      </c>
+      <c r="D13" s="16">
+        <v>46204</v>
+      </c>
+      <c r="E13" s="16">
+        <v>46260</v>
+      </c>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="23"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="18"/>
+      <c r="L13" s="18"/>
+      <c r="M13" s="18"/>
+      <c r="N13" s="18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="23"/>
+      <c r="I14" s="23"/>
+      <c r="J14" s="23"/>
+      <c r="K14" s="23"/>
+      <c r="L14" s="23"/>
+      <c r="M14" s="23"/>
+      <c r="N14" s="23"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="15">
+        <v>50</v>
+      </c>
+      <c r="D15" s="16">
+        <v>46204</v>
+      </c>
+      <c r="E15" s="16">
+        <v>46260</v>
+      </c>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="18"/>
+      <c r="K15" s="18"/>
+      <c r="L15" s="18"/>
+      <c r="M15" s="18"/>
+      <c r="N15" s="18"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="15">
+        <v>10</v>
+      </c>
+      <c r="D16" s="16">
+        <v>46204</v>
+      </c>
+      <c r="E16" s="16">
+        <v>46260</v>
+      </c>
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="23"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="18"/>
+      <c r="K16" s="18"/>
+      <c r="L16" s="18"/>
+      <c r="M16" s="23"/>
+      <c r="N16" s="23"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="15">
+        <v>20</v>
+      </c>
+      <c r="D17" s="16">
+        <v>46204</v>
+      </c>
+      <c r="E17" s="16">
+        <v>46260</v>
+      </c>
+      <c r="F17" s="23"/>
+      <c r="G17" s="23"/>
+      <c r="H17" s="23"/>
+      <c r="I17" s="23"/>
+      <c r="J17" s="18"/>
+      <c r="K17" s="18"/>
+      <c r="L17" s="18"/>
+      <c r="M17" s="18"/>
+      <c r="N17" s="18"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="C7:C9">
+    <cfRule type="dataBar" priority="3">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="100"/>
+        <color theme="3" tint="0.249977111117893"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{2C96338C-A9BE-4F45-8170-7E450E0DAC23}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C11:C13">
+    <cfRule type="dataBar" priority="2">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="100"/>
+        <color theme="3" tint="0.249977111117893"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{D5186038-07B5-4495-93AF-5897F02ABA8C}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C15:C17">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="100"/>
+        <color theme="3" tint="0.249977111117893"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{68A1F767-5B4E-4078-8747-D74667E44B28}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{2C96338C-A9BE-4F45-8170-7E450E0DAC23}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>100</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>C7:C9</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{D5186038-07B5-4495-93AF-5897F02ABA8C}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>100</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>C11:C13</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{68A1F767-5B4E-4078-8747-D74667E44B28}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>100</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>C15:C17</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
